--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -413,197 +413,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>valLiquidado</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valPagoRestos</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valSuplementado</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>valPagoExercicio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>valCanceladoReserva</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>valDescongelado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>valReservado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>valEmpenhadoLiquido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>valTotalEmpenhado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>valReservadoLiquido</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>valAnuladoEmpenho</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>valDisponivel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>valOrcadoInicial</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>valCongelado</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>valReduzido</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>valOrcadoAtualizado</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>contrato_gestao</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>secretaria</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>dotacao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>dotacao_exclusiva</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>valLiquidado</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>valPagoRestos</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>valSuplementado</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>valPagoExercicio</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>valCanceladoReserva</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>valDescongelado</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>valReservado</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>valEmpenhadoLiquido</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>valTotalEmpenhado</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>valReservadoLiquido</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>valAnuladoEmpenho</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>valDisponivel</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>valOrcadoInicial</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>valCongelado</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>valReduzido</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>valOrcadoAtualizado</t>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>data_hora_extracao</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SMDET</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SMDET</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>27603582.69</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3765000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27603582.69</v>
       </c>
       <c r="E2" t="n">
-        <v>27603582.69</v>
+        <v>31815317.31</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3765000</v>
+        <v>94999217.31</v>
       </c>
       <c r="H2" t="n">
-        <v>27603582.69</v>
+        <v>59418900</v>
       </c>
       <c r="I2" t="n">
-        <v>31815317.31</v>
+        <v>79418900</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>63183900</v>
       </c>
       <c r="K2" t="n">
-        <v>94999217.31</v>
+        <v>20000000</v>
       </c>
       <c r="L2" t="n">
+        <v>63183900</v>
+      </c>
+      <c r="M2" t="n">
         <v>59418900</v>
       </c>
-      <c r="M2" t="n">
-        <v>79418900</v>
-      </c>
       <c r="N2" t="n">
-        <v>63183900</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>63183900</v>
       </c>
-      <c r="Q2" t="n">
-        <v>59418900</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>63183900</v>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>SMDET</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SMDET</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="A3" t="n">
+        <v>2247234.98</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -612,19 +616,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="K3" t="n">
-        <v>4494470</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>4494470</v>
@@ -633,7 +637,7 @@
         <v>4494470</v>
       </c>
       <c r="N3" t="n">
-        <v>4494470</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -641,67 +645,72 @@
       <c r="P3" t="n">
         <v>4494470</v>
       </c>
-      <c r="Q3" t="n">
-        <v>4494470</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4494470</v>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SMSUB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SMSUB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>98.12.15.451.4020.3350.44905108.08.1.759.0402</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+      <c r="A4" t="n">
+        <v>3494910.92</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3494910.92</v>
       </c>
       <c r="E4" t="n">
-        <v>3494910.92</v>
+        <v>10570581.21</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>28209946.43</v>
       </c>
       <c r="H4" t="n">
-        <v>3494910.92</v>
+        <v>15849427.13</v>
       </c>
       <c r="I4" t="n">
-        <v>10570581.21</v>
+        <v>15849427.13</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>17639365.22</v>
       </c>
       <c r="K4" t="n">
-        <v>28209946.43</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15849427.13</v>
+        <v>20353249</v>
       </c>
       <c r="M4" t="n">
-        <v>15849427.13</v>
+        <v>20353249</v>
       </c>
       <c r="N4" t="n">
-        <v>17639365.22</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -709,85 +718,101 @@
       <c r="P4" t="n">
         <v>20353249</v>
       </c>
-      <c r="Q4" t="n">
-        <v>20353249</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>20353249</v>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>SMSUB</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>SMSUB</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>98.12.15.451.4020.3350.44905108.08.1.759.0402</t>
+        </is>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>136057060.35</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>130397580.38</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23850125.45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14675458.95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>285929081.17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>240512622.29</v>
+      </c>
+      <c r="I5" t="n">
+        <v>270999628.31</v>
+      </c>
+      <c r="J5" t="n">
+        <v>262078955.72</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30487006.02</v>
+      </c>
+      <c r="L5" t="n">
+        <v>473621350.95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>490748772</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30900000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>902880</v>
+      </c>
+      <c r="P5" t="n">
+        <v>489845892</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>SMTUR</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>SMTUR</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
         </is>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>135197124.83</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>130397580.38</v>
-      </c>
-      <c r="I5" t="n">
-        <v>23850125.45</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14675458.95</v>
-      </c>
-      <c r="K5" t="n">
-        <v>285929081.17</v>
-      </c>
-      <c r="L5" t="n">
-        <v>240512622.29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>270999628.31</v>
-      </c>
-      <c r="N5" t="n">
-        <v>262078955.72</v>
-      </c>
-      <c r="O5" t="n">
-        <v>30487006.02</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473621350.95</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>490748772</v>
-      </c>
-      <c r="R5" t="n">
-        <v>30900000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>902880</v>
-      </c>
-      <c r="T5" t="n">
-        <v>489845892</v>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,11 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>saldo_dotacao</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>data_hora_extracao</t>
         </is>
       </c>
@@ -590,9 +595,12 @@
       <c r="T2" t="b">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>05/05/2026 16:35:43</t>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -663,9 +671,12 @@
       <c r="T3" t="b">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>05/05/2026 16:35:43</t>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -736,9 +747,12 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>05/05/2026 16:35:43</t>
+      <c r="U4" t="n">
+        <v>2713883.780000001</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -765,10 +779,10 @@
         <v>285929081.17</v>
       </c>
       <c r="H5" t="n">
-        <v>240512622.29</v>
+        <v>240662622.29</v>
       </c>
       <c r="I5" t="n">
-        <v>270999628.31</v>
+        <v>271149628.31</v>
       </c>
       <c r="J5" t="n">
         <v>262078955.72</v>
@@ -809,9 +823,12 @@
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>05/05/2026 16:35:43</t>
+      <c r="U5" t="n">
+        <v>211542395.23</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -530,7 +530,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>27603582.69</v>
+        <v>49413581.23</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>94999217.31</v>
       </c>
       <c r="H2" t="n">
-        <v>59418900</v>
+        <v>61918900</v>
       </c>
       <c r="I2" t="n">
-        <v>79418900</v>
+        <v>81918900</v>
       </c>
       <c r="J2" t="n">
         <v>63183900</v>
@@ -579,7 +579,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>SMDET</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -676,13 +676,13 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3494910.92</v>
+        <v>3670725.49</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -752,13 +752,13 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136057060.35</v>
+        <v>140357060.35</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>130397580.38</v>
+        <v>134143552.46</v>
       </c>
       <c r="E5" t="n">
         <v>23850125.45</v>
@@ -779,10 +779,10 @@
         <v>285929081.17</v>
       </c>
       <c r="H5" t="n">
-        <v>240662622.29</v>
+        <v>240722622.29</v>
       </c>
       <c r="I5" t="n">
-        <v>271149628.31</v>
+        <v>271209628.31</v>
       </c>
       <c r="J5" t="n">
         <v>262078955.72</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -419,102 +419,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>contrato_gestao</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>secretaria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dotacao</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dotacao_exclusiva</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>valOrcadoInicial</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>valSuplementado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>valReduzido</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>valOrcadoAtualizado</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>valCongelado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>valDescongelado</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>valDisponivel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>valReservado</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>valCanceladoReserva</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>valReservadoLiquido</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>valTotalEmpenhado</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>valAnuladoEmpenho</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>valEmpenhadoLiquido</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>valLiquidado</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>valPagoExercicio</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>valPagoRestos</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>valSuplementado</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>valPagoExercicio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>valCanceladoReserva</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>valDescongelado</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>valReservado</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>valEmpenhadoLiquido</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>valTotalEmpenhado</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>valReservadoLiquido</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>valAnuladoEmpenho</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>valDisponivel</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>valOrcadoInicial</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>valCongelado</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>valReduzido</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>valOrcadoAtualizado</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>contrato_gestao</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>secretaria</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>dotacao</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>dotacao_exclusiva</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -529,222 +529,222 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SMDET - ADE SAMPA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SMDET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>59418900</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3765000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>63183900</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>63183900</v>
+      </c>
+      <c r="L2" t="n">
+        <v>94999217.31</v>
+      </c>
+      <c r="M2" t="n">
+        <v>31815317.31</v>
+      </c>
+      <c r="N2" t="n">
+        <v>63183900</v>
+      </c>
+      <c r="O2" t="n">
+        <v>81918900</v>
+      </c>
+      <c r="P2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>61918900</v>
+      </c>
+      <c r="R2" t="n">
         <v>49413581.23</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3765000</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="S2" t="n">
         <v>27603582.69</v>
       </c>
-      <c r="E2" t="n">
-        <v>31815317.31</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>94999217.31</v>
-      </c>
-      <c r="H2" t="n">
-        <v>61918900</v>
-      </c>
-      <c r="I2" t="n">
-        <v>81918900</v>
-      </c>
-      <c r="J2" t="n">
-        <v>63183900</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>63183900</v>
-      </c>
-      <c r="M2" t="n">
-        <v>59418900</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>63183900</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>SMDET - ADE SAMPA</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>SMDET</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="T2" t="b">
-        <v>1</v>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2247234.98</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4494470</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>4494470</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>4494470</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4494470</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>4494470</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>4494470</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4494470</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4494470</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>SMDET - VAI TEC</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>30.10.11.334.4012.4315.33508500.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="T3" t="b">
-        <v>1</v>
+      <c r="R3" t="n">
+        <v>2247234.98</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2247234.98</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SMSUB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SMSUB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>98.12.15.451.4020.3350.44905108.08.1.759.0402</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20353249</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20353249</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20353249</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28209946.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10570581.21</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17639365.22</v>
+      </c>
+      <c r="O4" t="n">
+        <v>15907317.93</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15907317.93</v>
+      </c>
+      <c r="R4" t="n">
         <v>3670725.49</v>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="S4" t="n">
         <v>3494910.92</v>
       </c>
-      <c r="E4" t="n">
-        <v>10570581.21</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>28209946.43</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15849427.13</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15849427.13</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17639365.22</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>20353249</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20353249</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>20353249</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>SMSUB</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>SMSUB</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>98.12.15.451.4020.3350.44905108.08.1.759.0402</t>
-        </is>
-      </c>
-      <c r="T4" t="b">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
@@ -752,83 +752,83 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>140357060.35</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>134143552.46</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>23850125.45</v>
+        <v>490748772</v>
       </c>
       <c r="F5" t="n">
+        <v>189098123.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>902880</v>
+      </c>
+      <c r="H5" t="n">
+        <v>678944015.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30900000</v>
+      </c>
+      <c r="J5" t="n">
         <v>14675458.95</v>
       </c>
-      <c r="G5" t="n">
-        <v>285929081.17</v>
-      </c>
-      <c r="H5" t="n">
-        <v>240722622.29</v>
-      </c>
-      <c r="I5" t="n">
-        <v>271209628.31</v>
-      </c>
-      <c r="J5" t="n">
-        <v>262078955.72</v>
-      </c>
       <c r="K5" t="n">
+        <v>662719474.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>468073760.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24164231.47</v>
+      </c>
+      <c r="N5" t="n">
+        <v>443909529.31</v>
+      </c>
+      <c r="O5" t="n">
+        <v>457041623.73</v>
+      </c>
+      <c r="P5" t="n">
         <v>30487006.02</v>
       </c>
-      <c r="L5" t="n">
-        <v>473621350.95</v>
-      </c>
-      <c r="M5" t="n">
-        <v>490748772</v>
-      </c>
-      <c r="N5" t="n">
-        <v>30900000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>902880</v>
-      </c>
-      <c r="P5" t="n">
-        <v>489845892</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>SMTUR</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>SMTUR</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>74.10.23.695.4009.2118.33903900.00.1.500.9001</t>
-        </is>
-      </c>
-      <c r="T5" t="b">
+      <c r="Q5" t="n">
+        <v>426554617.71</v>
+      </c>
+      <c r="R5" t="n">
+        <v>140749060.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>138143552.46</v>
+      </c>
+      <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>211542395.23</v>
+        <v>218809945.14</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -590,7 +590,7 @@
         <v>49413581.23</v>
       </c>
       <c r="S2" t="n">
-        <v>27603582.69</v>
+        <v>49413581.23</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -724,10 +724,10 @@
         <v>28209946.43</v>
       </c>
       <c r="M4" t="n">
-        <v>10570581.21</v>
+        <v>11481670.05</v>
       </c>
       <c r="N4" t="n">
-        <v>17639365.22</v>
+        <v>16728276.38</v>
       </c>
       <c r="O4" t="n">
         <v>15907317.93</v>
@@ -739,20 +739,20 @@
         <v>15907317.93</v>
       </c>
       <c r="R4" t="n">
-        <v>3670725.49</v>
+        <v>4988461.73</v>
       </c>
       <c r="S4" t="n">
-        <v>3494910.92</v>
+        <v>3844287.52</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2713883.780000001</v>
+        <v>3624972.619999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -779,13 +779,13 @@
         <v>490748772</v>
       </c>
       <c r="F5" t="n">
-        <v>189098123.5</v>
+        <v>208598123.5</v>
       </c>
       <c r="G5" t="n">
-        <v>902880</v>
+        <v>1059495.12</v>
       </c>
       <c r="H5" t="n">
-        <v>678944015.5</v>
+        <v>698287400.38</v>
       </c>
       <c r="I5" t="n">
         <v>30900000</v>
@@ -794,41 +794,41 @@
         <v>14675458.95</v>
       </c>
       <c r="K5" t="n">
-        <v>662719474.45</v>
+        <v>682062859.33</v>
       </c>
       <c r="L5" t="n">
-        <v>468073760.78</v>
+        <v>502288777.98</v>
       </c>
       <c r="M5" t="n">
-        <v>24164231.47</v>
+        <v>26662807.47</v>
       </c>
       <c r="N5" t="n">
-        <v>443909529.31</v>
+        <v>475625970.51</v>
       </c>
       <c r="O5" t="n">
-        <v>457041623.73</v>
+        <v>458259385.12</v>
       </c>
       <c r="P5" t="n">
         <v>30487006.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>426554617.71</v>
+        <v>427772379.1</v>
       </c>
       <c r="R5" t="n">
-        <v>140749060.33</v>
+        <v>337157372.33</v>
       </c>
       <c r="S5" t="n">
-        <v>138143552.46</v>
+        <v>319007417.46</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>218809945.14</v>
+        <v>206436888.8200001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>

--- a/base_execucao/execucao.xlsx
+++ b/base_execucao/execucao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,13 +551,13 @@
         <v>59418900</v>
       </c>
       <c r="F2" t="n">
-        <v>3765000</v>
+        <v>5565000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>63183900</v>
+        <v>64983900</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -566,16 +566,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>63183900</v>
+        <v>64983900</v>
       </c>
       <c r="L2" t="n">
-        <v>94999217.31</v>
+        <v>96799217.31</v>
       </c>
       <c r="M2" t="n">
         <v>31815317.31</v>
       </c>
       <c r="N2" t="n">
-        <v>63183900</v>
+        <v>64983900</v>
       </c>
       <c r="O2" t="n">
         <v>81918900</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -739,10 +739,10 @@
         <v>15907317.93</v>
       </c>
       <c r="R4" t="n">
-        <v>4988461.73</v>
+        <v>6128822.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3844287.52</v>
+        <v>5853939.58</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -752,7 +752,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -779,13 +779,13 @@
         <v>490748772</v>
       </c>
       <c r="F5" t="n">
-        <v>208598123.5</v>
+        <v>209798123.5</v>
       </c>
       <c r="G5" t="n">
         <v>1059495.12</v>
       </c>
       <c r="H5" t="n">
-        <v>698287400.38</v>
+        <v>699487400.38</v>
       </c>
       <c r="I5" t="n">
         <v>30900000</v>
@@ -794,41 +794,117 @@
         <v>14675458.95</v>
       </c>
       <c r="K5" t="n">
-        <v>682062859.33</v>
+        <v>683262859.33</v>
       </c>
       <c r="L5" t="n">
-        <v>502288777.98</v>
+        <v>507712339.1</v>
       </c>
       <c r="M5" t="n">
-        <v>26662807.47</v>
+        <v>26665607.47</v>
       </c>
       <c r="N5" t="n">
-        <v>475625970.51</v>
+        <v>481046731.63</v>
       </c>
       <c r="O5" t="n">
-        <v>458259385.12</v>
+        <v>496705402.05</v>
       </c>
       <c r="P5" t="n">
         <v>30487006.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>427772379.1</v>
+        <v>466218396.03</v>
       </c>
       <c r="R5" t="n">
-        <v>337157372.33</v>
+        <v>367052868.42</v>
       </c>
       <c r="S5" t="n">
-        <v>319007417.46</v>
+        <v>346291060.36</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>206436888.8200001</v>
+        <v>202216127.7</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25.10.13.392.4032.6960.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
